--- a/output/interpretation_high_attention_cluster_MKM_MKMonVAE/centroidi_annotated_27_risk1_2024_pr_interpretation_high_attention_MKMonVAE.xlsx
+++ b/output/interpretation_high_attention_cluster_MKM_MKMonVAE/centroidi_annotated_27_risk1_2024_pr_interpretation_high_attention_MKMonVAE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\lavoro\07Massaciuccoli\risk_assessment\r_scripts\r_03UnsupervisedRiskAssessment\output\MultiKmeans_on_VAE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\lavoro\github\TerrestrialEcosystemRiskAssessment\output\interpretation_high_attention_cluster_MKM_MKMonVAE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64283492-4E99-416F-890F-EF3A0F40BD4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBAA3AF0-95F8-4888-8537-54B9300603E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38510" yWindow="-11090" windowWidth="38620" windowHeight="21220" firstSheet="1" activeTab="1" xr2:uid="{78E96C89-25A9-4686-8FAA-077920FB5BB5}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="129">
   <si>
     <t>centroid_id</t>
   </si>
@@ -544,6 +544,9 @@
   </si>
   <si>
     <t>Average</t>
+  </si>
+  <si>
+    <t>closer attention</t>
   </si>
 </sst>
 </file>
@@ -4484,7 +4487,7 @@
         <v>27</v>
       </c>
       <c r="AO2" t="s">
-        <v>78</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:41" hidden="1" x14ac:dyDescent="0.35">
@@ -4608,7 +4611,7 @@
         <v>25</v>
       </c>
       <c r="AO3" t="s">
-        <v>78</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:41" x14ac:dyDescent="0.35">
@@ -4735,7 +4738,7 @@
         <v>25</v>
       </c>
       <c r="AO4" t="s">
-        <v>78</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:41" hidden="1" x14ac:dyDescent="0.35">
@@ -4859,7 +4862,7 @@
         <v>27</v>
       </c>
       <c r="AO5" t="s">
-        <v>78</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:41" x14ac:dyDescent="0.35">
@@ -4986,7 +4989,7 @@
         <v>25</v>
       </c>
       <c r="AO6" t="s">
-        <v>78</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:41" x14ac:dyDescent="0.35">
@@ -5113,7 +5116,7 @@
         <v>27</v>
       </c>
       <c r="AO7" t="s">
-        <v>78</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:41" hidden="1" x14ac:dyDescent="0.35">
@@ -5240,7 +5243,7 @@
         <v>27</v>
       </c>
       <c r="AO8" t="s">
-        <v>78</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" spans="1:41" x14ac:dyDescent="0.35">
@@ -5344,7 +5347,7 @@
         <v>2.2428620258274027E-2</v>
       </c>
       <c r="AO10" t="s">
-        <v>78</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16" spans="1:41" x14ac:dyDescent="0.35">
